--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F08C74-A21E-49AD-9F73-6416A6D2BC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986D6B6C-311A-468C-A8AA-0E20099AD1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-16965" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="맛집데이터" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>이름</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>korean</t>
-  </si>
-  <si>
-    <t>chinese</t>
   </si>
   <si>
     <t>japanese</t>
@@ -137,10 +134,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026.05.21</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>후기</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -155,6 +148,63 @@
   </si>
   <si>
     <t>가성비, 맛집, 혼밥, 혼술, 순대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동/괴정동 동네에 있는 작은 술집입니다. 파스타, 감바스 등 맛있는 안주와 함께 칵테일을 먹을 수 있는 곳입니다. 특히, 문문 하이볼은 가격도 좋지만 맛도 좋아서 매우 추천해 드립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문문 하이볼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>월,화,수,목,금,토 19:00~01:00
+일요일 휴무</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,000~30,000원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1418-7710</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.05.19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동과 바짝 붙어있는 괴정동에 있는 술집으로 집 근처에 있어서 자주 가는 곳입니다. 하이볼이 마시고 싶을 때, 이곳에서 한번 마셔보세요. 분위기도 좋고 안주도 맛있고, 다 좋습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한적한 도로 한쪽에 있습니다. 주차는 가능한 곳에 하시고 걸어가시는게 좋습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분위기, 맛집, 하이볼, 혼술</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문문</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/search/%EB%AC%B8%EB%AC%B8?c=15.00,0,0,0,dh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전 서구 용문동 [268-1]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문문1, 문문2, 문문3, 문문4, 문문5, 문문6, 문문7, 문문8</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -162,7 +212,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +232,14 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -222,10 +280,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,9 +292,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -599,7 +662,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>13</v>
@@ -625,44 +688,44 @@
     </row>
     <row r="2" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F2" s="2">
         <v>5</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="M2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="O2" s="2">
         <v>5</v>
@@ -674,45 +737,83 @@
         <v>4</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
+      <c r="U2" s="3"/>
     </row>
     <row r="3" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="F3" s="2">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="4" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -739,7 +840,7 @@
     <row r="5" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -766,7 +867,7 @@
     <row r="6" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -793,7 +894,7 @@
     <row r="7" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -824,6 +925,9 @@
       <formula1>"korean,chinese,japanese,cafe,bar,lunch"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="U3" r:id="rId1" xr:uid="{1252D5A7-554E-4533-A24C-BF451AB9C1B2}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986D6B6C-311A-468C-A8AA-0E20099AD1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32206E53-5763-4C7E-994A-D5FB211E0DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
   <si>
     <t>이름</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>korean</t>
-  </si>
-  <si>
-    <t>japanese</t>
   </si>
   <si>
     <t>cafe</t>
@@ -205,6 +202,75 @@
   </si>
   <si>
     <t>문문1, 문문2, 문문3, 문문4, 문문5, 문문6, 문문7, 문문8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모정득옛날고기집</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>살짝 양념되어 있는 소 갈비살을 파는 소고기 집으로, 고기도 맛있지만 사이드 메뉴도 정말 맛있는 집이다. 소고기 양도 많고 가격도 나쁘지 않다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>소갈비살, 열무비빔밥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전 서구 용문동 [590-30]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>월, 화, 수, 목, 금, 토 16:00~01:00
+라스트 오더 00:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,000원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1454-0092</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동에는 맛있는 고깃집이 많습니다. 여기도 그 고깃집중 하나입니다. 특히, 소갈비살은 여기가 거의 유일하며, 소고기 먹고 싶을땐 꼭 여기로 옵니다. 소고기도 당연히 맛있지만 사이드 메뉴 중에 열무비빔밥이 정말 맛있습니다. 열무 비빔밥도 놓치지 마시고 꼭 드셔보세요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동 내부는 주차하기가 어렵습니다. 주변 주차 할 수 있는 곳에 주차하시고 걸어 오는 것을 추천합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>소고기, 소갈비살, 열무비빔밥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모정득1, 모정득2, 모정득3, 모정득4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>moonmoon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mojung</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥당1, 옥당2, 옥당3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/search/%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80/place/1599860073?c=15.00,0,0,0,dh&amp;isCorrectAnswer=true&amp;placePath=/home?fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172222&amp;locale=ko&amp;svcName=map_pcv5&amp;searchText=%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80&amp;fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172222&amp;locale=ko&amp;svcName=map_pcv5&amp;searchText=%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/1245143410?c=15.00,0,0,0,dh&amp;placePath=/home?from=map&amp;fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172223&amp;locale=ko&amp;svcName=map_pcv5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>oukdang</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -662,7 +728,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>13</v>
@@ -688,44 +754,46 @@
     </row>
     <row r="2" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O2" s="2">
         <v>5</v>
@@ -737,56 +805,60 @@
         <v>4</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="3"/>
+      <c r="T2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="3" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="F3" s="2">
         <v>5</v>
       </c>
-      <c r="G3" s="2">
-        <v>0</v>
+      <c r="G3" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="M3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="O3" s="2">
         <v>5</v>
@@ -798,49 +870,87 @@
         <v>5</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="T3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="F4" s="2">
         <v>5</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="2">
+        <v>5</v>
+      </c>
+      <c r="P4" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>3</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -867,7 +977,7 @@
     <row r="6" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -894,7 +1004,7 @@
     <row r="7" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -927,6 +1037,8 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="U3" r:id="rId1" xr:uid="{1252D5A7-554E-4533-A24C-BF451AB9C1B2}"/>
+    <hyperlink ref="U2" r:id="rId2" display="https://map.naver.com/p/search/%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80/place/1599860073?c=15.00,0,0,0,dh&amp;isCorrectAnswer=true&amp;placePath=/home?fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172222&amp;locale=ko&amp;svcName=map_pcv5&amp;searchText=%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80&amp;fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172222&amp;locale=ko&amp;svcName=map_pcv5&amp;searchText=%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80" xr:uid="{26E5D53C-C932-4DA8-B8F3-36312CB33FBA}"/>
+    <hyperlink ref="U4" r:id="rId3" xr:uid="{23BD431F-91C9-433A-86CE-D41E23DF7555}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32206E53-5763-4C7E-994A-D5FB211E0DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289509CB-365F-4A68-9850-79244D59D7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>이름</t>
   </si>
@@ -271,6 +271,10 @@
   </si>
   <si>
     <t>oukdang</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/vyodnYktKqQ?feature=share</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -350,7 +354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -359,6 +363,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -664,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -687,7 +694,7 @@
     <col min="21" max="21" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -752,7 +759,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -816,8 +823,11 @@
       <c r="U2" s="3" t="s">
         <v>65</v>
       </c>
+      <c r="V2" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="3" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>47</v>
       </c>
@@ -882,7 +892,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>51</v>
       </c>
@@ -947,7 +957,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>21</v>
@@ -974,7 +984,7 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>22</v>
@@ -1001,7 +1011,7 @@
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>23</v>
@@ -1039,6 +1049,7 @@
     <hyperlink ref="U3" r:id="rId1" xr:uid="{1252D5A7-554E-4533-A24C-BF451AB9C1B2}"/>
     <hyperlink ref="U2" r:id="rId2" display="https://map.naver.com/p/search/%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80/place/1599860073?c=15.00,0,0,0,dh&amp;isCorrectAnswer=true&amp;placePath=/home?fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172222&amp;locale=ko&amp;svcName=map_pcv5&amp;searchText=%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80&amp;fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172222&amp;locale=ko&amp;svcName=map_pcv5&amp;searchText=%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80" xr:uid="{26E5D53C-C932-4DA8-B8F3-36312CB33FBA}"/>
     <hyperlink ref="U4" r:id="rId3" xr:uid="{23BD431F-91C9-433A-86CE-D41E23DF7555}"/>
+    <hyperlink ref="V2" r:id="rId4" xr:uid="{ACEE9FC8-5687-4A76-8655-7535136FD004}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289509CB-365F-4A68-9850-79244D59D7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3521640-1CD9-41C8-83E4-D6EB3B9AF690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
   <si>
     <t>이름</t>
   </si>
@@ -275,6 +275,10 @@
   </si>
   <si>
     <t>https://youtube.com/shorts/vyodnYktKqQ?feature=share</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/6_egdy3bG9w?feature=share</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -354,7 +358,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -367,6 +371,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -956,6 +963,9 @@
       <c r="U4" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="V4" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="5" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -1050,6 +1060,7 @@
     <hyperlink ref="U2" r:id="rId2" display="https://map.naver.com/p/search/%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80/place/1599860073?c=15.00,0,0,0,dh&amp;isCorrectAnswer=true&amp;placePath=/home?fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172222&amp;locale=ko&amp;svcName=map_pcv5&amp;searchText=%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80&amp;fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172222&amp;locale=ko&amp;svcName=map_pcv5&amp;searchText=%EC%98%A5%EB%8B%B9%EC%88%9C%EB%8C%80" xr:uid="{26E5D53C-C932-4DA8-B8F3-36312CB33FBA}"/>
     <hyperlink ref="U4" r:id="rId3" xr:uid="{23BD431F-91C9-433A-86CE-D41E23DF7555}"/>
     <hyperlink ref="V2" r:id="rId4" xr:uid="{ACEE9FC8-5687-4A76-8655-7535136FD004}"/>
+    <hyperlink ref="V4" r:id="rId5" xr:uid="{6F5EF022-98D2-4971-9976-8E4913002DC1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3521640-1CD9-41C8-83E4-D6EB3B9AF690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F9F26E-AD35-4730-A1C6-0C4668CF763E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
   <si>
     <t>이름</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>korean</t>
-  </si>
-  <si>
-    <t>cafe</t>
   </si>
   <si>
     <t>bar</t>
@@ -279,6 +276,67 @@
   </si>
   <si>
     <t>https://youtube.com/shorts/6_egdy3bG9w?feature=share</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>명량생조개손칼국수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물총칼국수 용문동 맛집입니다. 국물이 얼큰하면서도 시원한 칼국수입니다. 해장으로도 매우 좋습니다. 면도 진짜 식감이 장난 아닙니다. 그뿐만 아니라 두루치기랑 수육도 팝니다. 이것도 맛있어요. 그리고 파전도 유명합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물총칼국수, 해물파전, 두부두루치기, 수육</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>merang</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전 서구 용문동 [590-21]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일, 화, 수, 목, 금, 토 11:00~21:00
+월요일 정기 휴무</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,000~15,000원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가게 앞 4자리 정도 있음.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>042-535-0990</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.05.20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동에서 먹을 수 있는 물총칼국수로 어느 동네에서 먹었던 물총칼국수 만큼 맛있다. 특히, 여기 칼국수면은 진짜 쫄깃하고, 국물도 시원한것도 있지만 해장이 확실하게 잘된다. 주변에서 술마시고 다음날 일어나서 해장하고 싶다면 꼭 가보도록해라. 이보다 시원하고 맛있고 해장 잘되는 칼국수는 없다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가게 앞에 4자리 정도 주차 장소가 있으니 편하게 오셔도 됩니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물총칼국수, 두부두루치기, 해물파전</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>명량생조개1, 명량생조개2, 명량생조개3, 명량생조개4, 명량생조개5, 멸량생조개6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/16277892?c=19.36,0,0,0,dh&amp;placePath=/home?from=map&amp;fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172328&amp;locale=ko&amp;svcName=map_pcv5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -742,7 +800,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>13</v>
@@ -768,46 +826,46 @@
     </row>
     <row r="2" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="2">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O2" s="2">
         <v>5</v>
@@ -819,128 +877,128 @@
         <v>4</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="T2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="V2" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="2">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="2">
-        <v>5</v>
-      </c>
-      <c r="P3" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>5</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="2">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="O4" s="2">
         <v>5</v>
@@ -952,52 +1010,90 @@
         <v>3</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="U4" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="F5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O5" s="2">
+        <v>5</v>
+      </c>
+      <c r="P5" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>3</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="6" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1024,7 +1120,7 @@
     <row r="7" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1061,6 +1157,7 @@
     <hyperlink ref="U4" r:id="rId3" xr:uid="{23BD431F-91C9-433A-86CE-D41E23DF7555}"/>
     <hyperlink ref="V2" r:id="rId4" xr:uid="{ACEE9FC8-5687-4A76-8655-7535136FD004}"/>
     <hyperlink ref="V4" r:id="rId5" xr:uid="{6F5EF022-98D2-4971-9976-8E4913002DC1}"/>
+    <hyperlink ref="U5" r:id="rId6" xr:uid="{7A4CA388-22AC-4012-8989-149B896D9110}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F9F26E-AD35-4730-A1C6-0C4668CF763E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75E5D4F-FCC2-495D-BB6E-8304463D5874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,11 +332,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>명량생조개1, 명량생조개2, 명량생조개3, 명량생조개4, 명량생조개5, 멸량생조개6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://map.naver.com/p/entry/place/16277892?c=19.36,0,0,0,dh&amp;placePath=/home?from=map&amp;fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605172328&amp;locale=ko&amp;svcName=map_pcv5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>명량생조개1, 명량생조개2, 명량생조개3, 명량생조개4, 명량생조개5, 명량생조개6</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1084,10 +1084,10 @@
         <v>81</v>
       </c>
       <c r="T5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">

--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75E5D4F-FCC2-495D-BB6E-8304463D5874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF5F421-88F2-4BB5-A7E9-4B852AC1A020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
   <si>
     <t>이름</t>
   </si>
@@ -170,10 +170,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026.05.19</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>용문동과 바짝 붙어있는 괴정동에 있는 술집으로 집 근처에 있어서 자주 가는 곳입니다. 하이볼이 마시고 싶을 때, 이곳에서 한번 마셔보세요. 분위기도 좋고 안주도 맛있고, 다 좋습니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -316,10 +312,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026.05.20</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>용문동에서 먹을 수 있는 물총칼국수로 어느 동네에서 먹었던 물총칼국수 만큼 맛있다. 특히, 여기 칼국수면은 진짜 쫄깃하고, 국물도 시원한것도 있지만 해장이 확실하게 잘된다. 주변에서 술마시고 다음날 일어나서 해장하고 싶다면 꼭 가보도록해라. 이보다 시원하고 맛있고 해장 잘되는 칼국수는 없다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -337,6 +329,86 @@
   </si>
   <si>
     <t>명량생조개1, 명량생조개2, 명량생조개3, 명량생조개4, 명량생조개5, 명량생조개6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chinese</t>
+  </si>
+  <si>
+    <t>조기종의 향미각</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조기종의 향미각은 용문동에서 가장 맛있는 짜장면과 짬뽕을 팔고 있습니다. 누구나 좋아하는 맛이며 언제가도 실패하지 않고, 자리도 많아서 기다리더라도 길게 기다리지 않아도 되는 맛집입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짬뽕, 짜장면</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>jogijong</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전 서구 용문동 [275-3]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>월, 수, 목, 금, 토, 일 11:00~21:00
+화요일 정기 휴무</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,000원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주차는 혼잡합니다. 가능하면 주변 원룸촌에 두고 걸어오세요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>042-536-8252</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>국물은 고기 짬뽕으로 걸걸하면서도 얼큰한데 건데기는 알꼬막이 올라가서 아주 조화롭습니다. 국물을 한번 먹기 시작하면 다 먹어야하는 중독되는 맛도 있습니다. 짜장면은 유니 짜장으로 간 고기가 아주 많이 들어가 있고, 면에 간이 잘 베어서 조화롭게 먹을 수 있습니다. 솔직히 여기 만큼 맛있는 짬뽕/짜장면을 먹어본적이 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11시에 맞춰서 가지말고 조금 더 일찍 가시면 좋습니다. 11시에 한번에 들어가지 않고 미리가면 미리 받아주더라고요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짬뽕, 알꼬막, 향미각, 유니짜장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조기종1, 조기종2, 조기종3, 조기종4, 조기종5, 조기종6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/search/%EC%A1%B0%EA%B8%B0%EC%A2%85%EC%9D%98%20%ED%96%A5%EB%AF%B8%EA%B0%81%20%EB%8C%80%EC%A0%84?c=15.44,0,0,0,dh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/lGewMQ6ww88?feature=share</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -388,7 +460,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -411,12 +483,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -432,6 +513,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -844,7 +928,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>27</v>
@@ -883,18 +967,18 @@
         <v>35</v>
       </c>
       <c r="T2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="V2" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>21</v>
@@ -912,10 +996,10 @@
         <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>38</v>
@@ -930,75 +1014,75 @@
         <v>40</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2">
+        <v>5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="2">
-        <v>5</v>
-      </c>
-      <c r="P3" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>5</v>
-      </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="T3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="2">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="O4" s="2">
         <v>5</v>
@@ -1010,63 +1094,63 @@
         <v>3</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="U4" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="2">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O5" s="2">
         <v>5</v>
@@ -1078,44 +1162,85 @@
         <v>3</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="F6" s="2">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="O6" s="2">
+        <v>5</v>
+      </c>
+      <c r="P6" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>3</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="7" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -1158,6 +1283,8 @@
     <hyperlink ref="V2" r:id="rId4" xr:uid="{ACEE9FC8-5687-4A76-8655-7535136FD004}"/>
     <hyperlink ref="V4" r:id="rId5" xr:uid="{6F5EF022-98D2-4971-9976-8E4913002DC1}"/>
     <hyperlink ref="U5" r:id="rId6" xr:uid="{7A4CA388-22AC-4012-8989-149B896D9110}"/>
+    <hyperlink ref="U6" r:id="rId7" xr:uid="{40B5A016-84D4-4023-B533-A49FFFCED5C1}"/>
+    <hyperlink ref="V6" r:id="rId8" xr:uid="{96ED8CA4-9248-4E52-8BE2-2D67F1713188}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF5F421-88F2-4BB5-A7E9-4B852AC1A020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8F647B-F548-491F-86F7-15FED862EF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,11 +132,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>용문동에서 제일 맛있는 순대국밥 집입니다. 순대국밥을 그냥 드시지 마시고, 상위에 있는 파 다대기와 함게 드십시오. 파 다대기를 적당량 국밥에 넣어서 빨갛게 먹으면 진짜 맛있습니다.
-개인적으로 모둠순대 하나 시키면 국물도 같이 주는데, 이거 하나 시켜서 막걸리랑 같이 먹는게 가장 좋더라고요. 대전 용문동 옥당순대 최고입니다.\</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>단 한번도 웨이팅 등 기다린적은 없습니다. 항상 언제가든 자리가 있으니 편하게 가보세요.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -170,10 +165,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>용문동과 바짝 붙어있는 괴정동에 있는 술집으로 집 근처에 있어서 자주 가는 곳입니다. 하이볼이 마시고 싶을 때, 이곳에서 한번 마셔보세요. 분위기도 좋고 안주도 맛있고, 다 좋습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>한적한 도로 한쪽에 있습니다. 주차는 가능한 곳에 하시고 걸어가시는게 좋습니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -227,10 +218,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>용문동에는 맛있는 고깃집이 많습니다. 여기도 그 고깃집중 하나입니다. 특히, 소갈비살은 여기가 거의 유일하며, 소고기 먹고 싶을땐 꼭 여기로 옵니다. 소고기도 당연히 맛있지만 사이드 메뉴 중에 열무비빔밥이 정말 맛있습니다. 열무 비빔밥도 놓치지 마시고 꼭 드셔보세요.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>용문동 내부는 주차하기가 어렵습니다. 주변 주차 할 수 있는 곳에 주차하시고 걸어 오는 것을 추천합니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -312,10 +299,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>용문동에서 먹을 수 있는 물총칼국수로 어느 동네에서 먹었던 물총칼국수 만큼 맛있다. 특히, 여기 칼국수면은 진짜 쫄깃하고, 국물도 시원한것도 있지만 해장이 확실하게 잘된다. 주변에서 술마시고 다음날 일어나서 해장하고 싶다면 꼭 가보도록해라. 이보다 시원하고 맛있고 해장 잘되는 칼국수는 없다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>가게 앞에 4자리 정도 주차 장소가 있으니 편하게 오셔도 됩니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -388,10 +371,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>국물은 고기 짬뽕으로 걸걸하면서도 얼큰한데 건데기는 알꼬막이 올라가서 아주 조화롭습니다. 국물을 한번 먹기 시작하면 다 먹어야하는 중독되는 맛도 있습니다. 짜장면은 유니 짜장으로 간 고기가 아주 많이 들어가 있고, 면에 간이 잘 베어서 조화롭게 먹을 수 있습니다. 솔직히 여기 만큼 맛있는 짬뽕/짜장면을 먹어본적이 없습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>11시에 맞춰서 가지말고 조금 더 일찍 가시면 좋습니다. 11시에 한번에 들어가지 않고 미리가면 미리 받아주더라고요.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -409,6 +388,32 @@
   </si>
   <si>
     <t>https://youtube.com/shorts/lGewMQ6ww88?feature=share</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동에서 제일 맛있는 순대국밥 집입니다. 순대국밥을 그냥 드시지 마시고, 상위에 있는 파 다대기와 함게 드십시오. 파 다대기를 적당량 국밥에 넣어서 빨갛게 먹으면 진짜 맛있습니다.
+개인적으로 모둠순대 하나 시키면 국물도 같이 주는데, 이거 하나 시켜서 막걸리랑 같이 먹는게 가장 좋더라고요. 대전 용문동 옥당순대 최고입니다.
+롯데백화점 성심당 주변에 있는 맛집중 하나로 성심당에 왔으면 점심엔 여기서 먹어보자.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동과 바짝 붙어있는 괴정동에 있는 술집으로 집 근처에 있어서 자주 가는 곳입니다. 하이볼이 마시고 싶을 때, 이곳에서 한번 마셔보세요. 분위기도 좋고 안주도 맛있고, 다 좋습니다.
+롯데백화점 성심당 주변에 있는 맛집중 하나로 성심당에 왔으면 점심엔 여기서 먹어보자.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동에는 맛있는 고깃집이 많습니다. 여기도 그 고깃집중 하나입니다. 특히, 소갈비살은 여기가 거의 유일하며, 소고기 먹고 싶을땐 꼭 여기로 옵니다. 소고기도 당연히 맛있지만 사이드 메뉴 중에 열무비빔밥이 정말 맛있습니다. 열무 비빔밥도 놓치지 마시고 꼭 드셔보세요.
+롯데백화점 성심당 주변에 있는 맛집중 하나로 성심당에 왔으면 점심엔 여기서 먹어보자.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동에서 먹을 수 있는 물총칼국수로 어느 동네에서 먹었던 물총칼국수 만큼 맛있다. 특히, 여기 칼국수면은 진짜 쫄깃하고, 국물도 시원한것도 있지만 해장이 확실하게 잘된다. 주변에서 술마시고 다음날 일어나서 해장하고 싶다면 꼭 가보도록해라. 이보다 시원하고 맛있고 해장 잘되는 칼국수는 없다.
+롯데백화점 성심당 주변에 있는 맛집중 하나로 성심당에 왔으면 점심엔 여기서 먹어보자.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>국물은 고기 짬뽕으로 걸걸하면서도 얼큰한데 건데기는 알꼬막이 올라가서 아주 조화롭습니다. 국물을 한번 먹기 시작하면 다 먹어야하는 중독되는 맛도 있습니다. 짜장면은 유니 짜장으로 간 고기가 아주 많이 들어가 있고, 면에 간이 잘 베어서 조화롭게 먹을 수 있습니다. 솔직히 여기 만큼 맛있는 짬뽕/짜장면을 먹어본적이 없습니다.
+롯데백화점 성심당 주변에 있는 맛집중 하나로 성심당에 왔으면 점심엔 여기서 먹어보자.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -928,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>27</v>
@@ -946,10 +951,10 @@
         <v>31</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="O2" s="2">
         <v>5</v>
@@ -961,128 +966,128 @@
         <v>4</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="T2" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="U2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="V2" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="2">
-        <v>5</v>
-      </c>
-      <c r="P3" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>5</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="2">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="O4" s="2">
         <v>5</v>
@@ -1094,63 +1099,63 @@
         <v>3</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="U4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="2">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="O5" s="2">
         <v>5</v>
@@ -1162,60 +1167,60 @@
         <v>3</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="2">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="O6" s="2">
         <v>5</v>
@@ -1227,19 +1232,19 @@
         <v>3</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">

--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8F647B-F548-491F-86F7-15FED862EF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588D003C-7F29-42BB-AFC9-F445C33A6D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="115">
   <si>
     <t>이름</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>bar</t>
-  </si>
-  <si>
-    <t>korean,lunch</t>
   </si>
   <si>
     <t>옥당순대</t>
@@ -414,6 +411,64 @@
   <si>
     <t>국물은 고기 짬뽕으로 걸걸하면서도 얼큰한데 건데기는 알꼬막이 올라가서 아주 조화롭습니다. 국물을 한번 먹기 시작하면 다 먹어야하는 중독되는 맛도 있습니다. 짜장면은 유니 짜장으로 간 고기가 아주 많이 들어가 있고, 면에 간이 잘 베어서 조화롭게 먹을 수 있습니다. 솔직히 여기 만큼 맛있는 짬뽕/짜장면을 먹어본적이 없습니다.
 롯데백화점 성심당 주변에 있는 맛집중 하나로 성심당에 왔으면 점심엔 여기서 먹어보자.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만담꾼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/search/%EB%A7%8C%EB%8B%B4%EA%BE%BC?c=15.00,0,0,0,dh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만담꾼1, 만담꾼,2, 만담꾼3, 만담꾼4, 만담꾼5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mandam</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전 서구 용문동 [590-25]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동의 만담꾼은 한번 가면 당골이 될 수 밖에 없는 맛집이며 술집입니다. 다양한 메유와 좋은 분위기는 데이트하기에도 너무나도 좋습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모둠튀김, 각종 안주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매일 17:00~05:00
+라스트 오더 03:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,000원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>식당 앞 주차 불가능합니다. 주변 원룸촌에 주차하시거나 대중교통 타고오세요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>070-7585-5641</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만담꾼의 안주는 모두 맛있다. 정말 자주가는 술집인데, 갈때마다 새로운 안주가 있어서 도전해보는 재미도 있다. 최근에 갔을때 먹었던 사이드 메뉴도 정말 맛있었다. 전복회 였던가. 아무튼 용문동 주변에서 살고 있다면 여길 안갈 수 없다. 꼭 친구 또는 연인과 함께 방문해보도록 하자.
+혹여나, 롯데백화점 성심당에 방문하고 술집을 찾는다면 만담꾼을 추천한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안주를 먹어보면 술을 마셔야 하니, 대중교통을 타고오는걸 추천합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용문동 술집, 맛집, 만담꾼, 튀김, 다양한 안주</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -889,7 +944,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>13</v>
@@ -915,46 +970,46 @@
     </row>
     <row r="2" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O2" s="2">
         <v>5</v>
@@ -966,128 +1021,128 @@
         <v>4</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="T2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="V2" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="2">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="O3" s="2">
-        <v>5</v>
-      </c>
-      <c r="P3" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>5</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="U3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="2">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O4" s="2">
         <v>5</v>
@@ -1099,63 +1154,63 @@
         <v>3</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="U4" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="2">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O5" s="2">
         <v>5</v>
@@ -1167,60 +1222,60 @@
         <v>3</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="2">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O6" s="2">
         <v>5</v>
@@ -1232,47 +1287,85 @@
         <v>3</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="V6" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="O7" s="2">
+        <v>5</v>
+      </c>
+      <c r="P7" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>5</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1290,6 +1383,7 @@
     <hyperlink ref="U5" r:id="rId6" xr:uid="{7A4CA388-22AC-4012-8989-149B896D9110}"/>
     <hyperlink ref="U6" r:id="rId7" xr:uid="{40B5A016-84D4-4023-B533-A49FFFCED5C1}"/>
     <hyperlink ref="V6" r:id="rId8" xr:uid="{96ED8CA4-9248-4E52-8BE2-2D67F1713188}"/>
+    <hyperlink ref="U7" r:id="rId9" xr:uid="{DE31F115-E973-43C8-900A-453F5A013B0E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/맛집데이터.xlsx
+++ b/맛집데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\000. 프로그램\009. mot_house_page\yongmun-food-blog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588D003C-7F29-42BB-AFC9-F445C33A6D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DABD955-1592-4F22-9EF0-D8B74A627CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-156" yWindow="17172" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,10 +422,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>만담꾼1, 만담꾼,2, 만담꾼3, 만담꾼4, 만담꾼5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>mandam</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -469,6 +465,10 @@
   </si>
   <si>
     <t>용문동 술집, 맛집, 만담꾼, 튀김, 다양한 안주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만담꾼1, 만담꾼2, 만담꾼3, 만담꾼4, 만담꾼5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1310,58 +1310,58 @@
         <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="2">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="2">
-        <v>5</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O7" s="2">
+        <v>5</v>
+      </c>
+      <c r="P7" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>5</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="O7" s="2">
-        <v>5</v>
-      </c>
-      <c r="P7" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>5</v>
-      </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="U7" s="3" t="s">
         <v>102</v>
